--- a/templates/ERC000051/metadata_template_ERC000051.xlsx
+++ b/templates/ERC000051/metadata_template_ERC000051.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$N$1:$N$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="613">
   <si>
     <t>alias</t>
   </si>
@@ -561,6 +561,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -724,6 +727,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2399,7 +2405,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2443,7 +2449,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2470,7 +2476,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3189,6 +3195,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3210,27 +3226,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3250,122 +3266,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3389,120 +3405,120 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -3540,1525 +3556,1525 @@
   <sheetData>
     <row r="1" spans="5:20">
       <c r="E1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="T1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="5:20">
       <c r="E2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="S2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="T2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="5:20">
       <c r="E3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="S3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="T3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="5:20">
       <c r="E4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="5:20">
       <c r="E5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="5:20">
       <c r="E6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="5:20">
       <c r="E7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="5:20">
       <c r="N8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="5:20">
       <c r="N9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="5:20">
       <c r="N10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="5:20">
       <c r="N11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" spans="5:20">
       <c r="N12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="5:20">
       <c r="N13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="5:20">
       <c r="N14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="5:20">
       <c r="N15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="5:20">
       <c r="N16" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="14:14">
       <c r="N17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="14:14">
       <c r="N18" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="14:14">
       <c r="N19" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="14:14">
       <c r="N20" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="14:14">
       <c r="N21" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="14:14">
       <c r="N22" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="14:14">
       <c r="N23" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="14:14">
       <c r="N24" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="14:14">
       <c r="N25" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="14:14">
       <c r="N26" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" spans="14:14">
       <c r="N27" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="14:14">
       <c r="N28" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="29" spans="14:14">
       <c r="N29" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="14:14">
       <c r="N30" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="31" spans="14:14">
       <c r="N31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" spans="14:14">
       <c r="N32" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="14:14">
       <c r="N33" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="14:14">
       <c r="N34" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="14:14">
       <c r="N35" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="14:14">
       <c r="N36" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="14:14">
       <c r="N37" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" spans="14:14">
       <c r="N38" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" spans="14:14">
       <c r="N39" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="40" spans="14:14">
       <c r="N40" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="14:14">
       <c r="N41" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" spans="14:14">
       <c r="N42" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" spans="14:14">
       <c r="N43" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" spans="14:14">
       <c r="N44" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="14:14">
       <c r="N45" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="14:14">
       <c r="N46" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="14:14">
       <c r="N47" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="14:14">
       <c r="N48" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="89" spans="14:14">
       <c r="N89" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="90" spans="14:14">
       <c r="N90" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="91" spans="14:14">
       <c r="N91" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="92" spans="14:14">
       <c r="N92" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="93" spans="14:14">
       <c r="N93" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="94" spans="14:14">
       <c r="N94" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="95" spans="14:14">
       <c r="N95" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="96" spans="14:14">
       <c r="N96" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="97" spans="14:14">
       <c r="N97" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="98" spans="14:14">
       <c r="N98" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="99" spans="14:14">
       <c r="N99" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="100" spans="14:14">
       <c r="N100" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101" spans="14:14">
       <c r="N101" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102" spans="14:14">
       <c r="N102" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="103" spans="14:14">
       <c r="N103" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="104" spans="14:14">
       <c r="N104" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="105" spans="14:14">
       <c r="N105" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="106" spans="14:14">
       <c r="N106" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="107" spans="14:14">
       <c r="N107" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="108" spans="14:14">
       <c r="N108" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="109" spans="14:14">
       <c r="N109" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="110" spans="14:14">
       <c r="N110" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="111" spans="14:14">
       <c r="N111" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="112" spans="14:14">
       <c r="N112" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="113" spans="14:14">
       <c r="N113" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="114" spans="14:14">
       <c r="N114" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="115" spans="14:14">
       <c r="N115" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="116" spans="14:14">
       <c r="N116" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="117" spans="14:14">
       <c r="N117" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="118" spans="14:14">
       <c r="N118" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="119" spans="14:14">
       <c r="N119" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="120" spans="14:14">
       <c r="N120" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="121" spans="14:14">
       <c r="N121" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="122" spans="14:14">
       <c r="N122" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="123" spans="14:14">
       <c r="N123" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="124" spans="14:14">
       <c r="N124" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="125" spans="14:14">
       <c r="N125" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="126" spans="14:14">
       <c r="N126" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="127" spans="14:14">
       <c r="N127" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="128" spans="14:14">
       <c r="N128" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="129" spans="14:14">
       <c r="N129" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="130" spans="14:14">
       <c r="N130" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="131" spans="14:14">
       <c r="N131" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="132" spans="14:14">
       <c r="N132" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="133" spans="14:14">
       <c r="N133" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="134" spans="14:14">
       <c r="N134" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="135" spans="14:14">
       <c r="N135" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="136" spans="14:14">
       <c r="N136" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="137" spans="14:14">
       <c r="N137" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="138" spans="14:14">
       <c r="N138" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="139" spans="14:14">
       <c r="N139" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="140" spans="14:14">
       <c r="N140" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="141" spans="14:14">
       <c r="N141" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="142" spans="14:14">
       <c r="N142" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="143" spans="14:14">
       <c r="N143" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="144" spans="14:14">
       <c r="N144" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="145" spans="14:14">
       <c r="N145" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="146" spans="14:14">
       <c r="N146" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="147" spans="14:14">
       <c r="N147" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="148" spans="14:14">
       <c r="N148" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="149" spans="14:14">
       <c r="N149" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="150" spans="14:14">
       <c r="N150" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="151" spans="14:14">
       <c r="N151" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="152" spans="14:14">
       <c r="N152" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="153" spans="14:14">
       <c r="N153" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="154" spans="14:14">
       <c r="N154" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="155" spans="14:14">
       <c r="N155" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="156" spans="14:14">
       <c r="N156" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="157" spans="14:14">
       <c r="N157" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="158" spans="14:14">
       <c r="N158" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="159" spans="14:14">
       <c r="N159" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="160" spans="14:14">
       <c r="N160" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="161" spans="14:14">
       <c r="N161" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="162" spans="14:14">
       <c r="N162" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="163" spans="14:14">
       <c r="N163" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="164" spans="14:14">
       <c r="N164" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="165" spans="14:14">
       <c r="N165" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="166" spans="14:14">
       <c r="N166" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="167" spans="14:14">
       <c r="N167" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="168" spans="14:14">
       <c r="N168" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="169" spans="14:14">
       <c r="N169" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="170" spans="14:14">
       <c r="N170" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="171" spans="14:14">
       <c r="N171" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="172" spans="14:14">
       <c r="N172" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="173" spans="14:14">
       <c r="N173" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="174" spans="14:14">
       <c r="N174" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="175" spans="14:14">
       <c r="N175" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="176" spans="14:14">
       <c r="N176" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="177" spans="14:14">
       <c r="N177" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="178" spans="14:14">
       <c r="N178" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="179" spans="14:14">
       <c r="N179" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="180" spans="14:14">
       <c r="N180" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="181" spans="14:14">
       <c r="N181" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="182" spans="14:14">
       <c r="N182" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="183" spans="14:14">
       <c r="N183" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="184" spans="14:14">
       <c r="N184" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="185" spans="14:14">
       <c r="N185" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="186" spans="14:14">
       <c r="N186" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="187" spans="14:14">
       <c r="N187" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="188" spans="14:14">
       <c r="N188" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="189" spans="14:14">
       <c r="N189" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="190" spans="14:14">
       <c r="N190" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="191" spans="14:14">
       <c r="N191" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="192" spans="14:14">
       <c r="N192" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="193" spans="14:14">
       <c r="N193" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="194" spans="14:14">
       <c r="N194" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="195" spans="14:14">
       <c r="N195" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="196" spans="14:14">
       <c r="N196" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="197" spans="14:14">
       <c r="N197" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="198" spans="14:14">
       <c r="N198" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="199" spans="14:14">
       <c r="N199" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="200" spans="14:14">
       <c r="N200" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="201" spans="14:14">
       <c r="N201" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="202" spans="14:14">
       <c r="N202" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="203" spans="14:14">
       <c r="N203" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="204" spans="14:14">
       <c r="N204" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="205" spans="14:14">
       <c r="N205" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="206" spans="14:14">
       <c r="N206" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="207" spans="14:14">
       <c r="N207" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="208" spans="14:14">
       <c r="N208" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="209" spans="14:14">
       <c r="N209" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="210" spans="14:14">
       <c r="N210" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="211" spans="14:14">
       <c r="N211" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="212" spans="14:14">
       <c r="N212" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="213" spans="14:14">
       <c r="N213" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="214" spans="14:14">
       <c r="N214" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="215" spans="14:14">
       <c r="N215" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="216" spans="14:14">
       <c r="N216" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="217" spans="14:14">
       <c r="N217" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="218" spans="14:14">
       <c r="N218" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="219" spans="14:14">
       <c r="N219" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="220" spans="14:14">
       <c r="N220" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="221" spans="14:14">
       <c r="N221" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="222" spans="14:14">
       <c r="N222" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="223" spans="14:14">
       <c r="N223" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="224" spans="14:14">
       <c r="N224" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="225" spans="14:14">
       <c r="N225" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="226" spans="14:14">
       <c r="N226" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="227" spans="14:14">
       <c r="N227" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="228" spans="14:14">
       <c r="N228" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="229" spans="14:14">
       <c r="N229" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="230" spans="14:14">
       <c r="N230" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="231" spans="14:14">
       <c r="N231" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="232" spans="14:14">
       <c r="N232" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="233" spans="14:14">
       <c r="N233" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="234" spans="14:14">
       <c r="N234" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="235" spans="14:14">
       <c r="N235" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="236" spans="14:14">
       <c r="N236" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="237" spans="14:14">
       <c r="N237" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="238" spans="14:14">
       <c r="N238" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="239" spans="14:14">
       <c r="N239" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="240" spans="14:14">
       <c r="N240" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="241" spans="14:14">
       <c r="N241" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="242" spans="14:14">
       <c r="N242" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="243" spans="14:14">
       <c r="N243" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="244" spans="14:14">
       <c r="N244" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="245" spans="14:14">
       <c r="N245" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="246" spans="14:14">
       <c r="N246" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="247" spans="14:14">
       <c r="N247" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="248" spans="14:14">
       <c r="N248" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="249" spans="14:14">
       <c r="N249" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="250" spans="14:14">
       <c r="N250" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="251" spans="14:14">
       <c r="N251" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="252" spans="14:14">
       <c r="N252" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="253" spans="14:14">
       <c r="N253" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="254" spans="14:14">
       <c r="N254" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="255" spans="14:14">
       <c r="N255" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="256" spans="14:14">
       <c r="N256" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="257" spans="14:14">
       <c r="N257" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="258" spans="14:14">
       <c r="N258" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="259" spans="14:14">
       <c r="N259" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="260" spans="14:14">
       <c r="N260" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="261" spans="14:14">
       <c r="N261" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="262" spans="14:14">
       <c r="N262" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="263" spans="14:14">
       <c r="N263" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="264" spans="14:14">
       <c r="N264" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="265" spans="14:14">
       <c r="N265" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="266" spans="14:14">
       <c r="N266" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="267" spans="14:14">
       <c r="N267" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="268" spans="14:14">
       <c r="N268" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="269" spans="14:14">
       <c r="N269" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="270" spans="14:14">
       <c r="N270" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="271" spans="14:14">
       <c r="N271" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="272" spans="14:14">
       <c r="N272" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="273" spans="14:14">
       <c r="N273" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="274" spans="14:14">
       <c r="N274" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="275" spans="14:14">
       <c r="N275" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="276" spans="14:14">
       <c r="N276" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="277" spans="14:14">
       <c r="N277" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="278" spans="14:14">
       <c r="N278" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="279" spans="14:14">
       <c r="N279" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="280" spans="14:14">
       <c r="N280" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="281" spans="14:14">
       <c r="N281" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="282" spans="14:14">
       <c r="N282" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="283" spans="14:14">
       <c r="N283" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="284" spans="14:14">
       <c r="N284" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="285" spans="14:14">
       <c r="N285" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="286" spans="14:14">
       <c r="N286" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="287" spans="14:14">
       <c r="N287" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="288" spans="14:14">
       <c r="N288" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="289" spans="14:14">
       <c r="N289" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000051/metadata_template_ERC000051.xlsx
+++ b/templates/ERC000051/metadata_template_ERC000051.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$N$1:$N$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$N$1:$N$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -30,14 +30,14 @@
     <definedName name="sampleorigin">'cv_sample'!$E$1:$E$7</definedName>
     <definedName name="sampletaxonname">'cv_sample'!$G$1:$G$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="wasthePDXmodelhumanised">'cv_sample'!$S$1:$S$3</definedName>
+    <definedName name="wasthepdxmodelhumanised">'cv_sample'!$S$1:$S$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="618">
   <si>
     <t>alias</t>
   </si>
@@ -561,6 +561,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -867,7 +870,7 @@
     <t>not provided</t>
   </si>
   <si>
-    <t>sample origin</t>
+    <t>sample_origin</t>
   </si>
   <si>
     <t>(Mandatory) Sample origin from which data deposited was generated, e.g. engrafted tumor</t>
@@ -891,7 +894,7 @@
     <t>tissue fragment</t>
   </si>
   <si>
-    <t>sample material</t>
+    <t>sample_material</t>
   </si>
   <si>
     <t>(Mandatory) Sample material from which data deposited was generated, e.g. tissue fragment. if unknown please select "not provided".</t>
@@ -903,13 +906,13 @@
     <t>Homo sapiens/Mus musculus xenograft</t>
   </si>
   <si>
-    <t>sample taxon name</t>
+    <t>sample_taxon_name</t>
   </si>
   <si>
     <t>(Mandatory) This field indicates if a sample is derived from a patient or xenograft. the following two options are available: homo sapiens/mus musculus xenograft (sample is from a xenograft derived tumor/cell culture) or homo sapiens (sample is from a patient tumor/cell culture). please ensure the selected value here is identical to the value in the 'scientific name' column/field.</t>
   </si>
   <si>
-    <t>sample unique ID</t>
+    <t>sample_unique_id</t>
   </si>
   <si>
     <t>(Mandatory) Unique identifier of the pdx or tumor sample, e.g. crc00003</t>
@@ -924,31 +927,31 @@
     <t>Recurrent Neoplasm</t>
   </si>
   <si>
-    <t>patient tumor type</t>
+    <t>patient_tumor_type</t>
   </si>
   <si>
     <t>(Mandatory) For a primary sample (a tumor at the original site of origin), please select “primary neoplasm” . for a metastatic sample (a tumor that has spread from its original (primary) site of growth to another site, close to or distant from the primary site), please select “metastatic neoplasm” . for a recurring neoplasm sample (neoplasm returning after a period of remission at the same location), please select “recurrent neoplasm” . if unknown tumor type, please select “not provided”.</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
   </si>
   <si>
-    <t>engrafted tumor sample passage</t>
+    <t>engrafted_tumor_sample_passage</t>
   </si>
   <si>
     <t>(Mandatory) If engrafted tumor sample, please indicate the passage from which the engrafted tumor sample was harvested (passage 0 must be the first engraftment in the mouse). please ensure you add a non-negative number greater than 0. if the sample origin is “patient tumor” please enter "not applicable". if passage number is unknown please enter "not provided”.</t>
   </si>
   <si>
-    <t>engrafted tumor collection site</t>
+    <t>engrafted_tumor_collection_site</t>
   </si>
   <si>
     <t>(Recommended) If the sample origin is “engrafted tumor”, please indicate the collection site from which the engrafted tumor sample was extracted (e.g. liver). please use terminology from ncit ontology: https://www.ebi.ac.uk/ols/ontologies/ncit. if unknown please select ncit term: “not available” ( http://purl.obolibrary.org/obo/ncit_c126101)”. if the sample origin is “patient tumor” please do not use this attribute.</t>
   </si>
   <si>
-    <t>patient tumor site of collection</t>
+    <t>patient_tumor_site_of_collection</t>
   </si>
   <si>
     <t>(Mandatory) Site of collection of the patient tissue sample which was extracted (can be different to primary site if it is a metastatic sample). please use ncit ontology, e.g. liver (http://purl.obolibrary.org/obo/ncit_c12392). if unknown please select ncit term: “not available” (http://purl.obolibrary.org/obo/ncit_c126101)</t>
@@ -1167,9 +1170,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1188,6 +1188,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1389,6 +1392,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1398,9 +1404,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1440,7 +1443,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1509,6 +1512,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1584,6 +1590,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1605,6 +1614,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1650,6 +1662,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1662,6 +1677,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1671,9 +1689,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1698,6 +1713,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1758,12 +1776,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -1818,31 +1836,31 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
   </si>
   <si>
-    <t>engraftment host strain name</t>
+    <t>engraftment_host_strain_name</t>
   </si>
   <si>
     <t>(Recommended) If the sample origin is “engrafted tumor”, please indicate the host mouse strain name from which the engrafted tumor sample was extracted (e.g. nod.cg-prkdcscid il2rgtm1wjl/szj). please use the following guidelines for the correct nomenclature format: http://www.informatics.jax.org/mgihome/nomen/strains.shtml#mice. if the sample origin is “patient tumor” please add "not applicable" and if unknown please add "not provided".</t>
   </si>
   <si>
-    <t>patient age at collection of tumor</t>
+    <t>patient_age_at_collection_of_tumor</t>
   </si>
   <si>
     <t>(Mandatory) Age in years of the patient when the tumor was extracted. please note this must be a whole number, e.g. 45</t>
   </si>
   <si>
-    <t>patient tumor diagnosis at time of collection</t>
+    <t>patient_tumor_diagnosis_at_time_of_collection</t>
   </si>
   <si>
     <t>(Mandatory) Patient tumor diagnosis at time of collection for engraftment in pdx model or organoid/cell derivation. please use terminology from ncit ontology: https://www.ebi.ac.uk/ols/ontologies/ncit - please note in ncit ontology, usually the “cancer” concept is represented with “malignant neoplasm”example: “lung cancer” is “malignant lung neoplasm” (http://purl.obolibrary.org/obo/ncit_c7377). if precise diagnosis is unknown, please use "neoplasm" (http://purl.obolibrary.org/obo/ncit_c3262)</t>
   </si>
   <si>
-    <t>patient tumor primary site</t>
+    <t>patient_tumor_primary_site</t>
   </si>
   <si>
     <t>(Mandatory) Site of the primary tumor where cancer originates (may not correspond to the site of the collected tissue sample). please use ncit ontology, e.g. colon (http://purl.obolibrary.org/obo/ncit_c12382). if unknown please select ncit term: “not available” ( http://purl.obolibrary.org/obo/ncit_c126101)</t>
@@ -1854,7 +1872,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>was the PDX model humanised?</t>
+    <t>was_the_pdx_model_humanised</t>
   </si>
   <si>
     <t>(Recommended) If the sample origin is “engrafted tumor”, please indicate if the host strain, from which the sample was extracted, has undergone human immune system reconstitution, using “yes” (model humanised) or “no” (model not humanised). if the sample origin is “patient tumor” please select "not applicable".</t>
@@ -1869,7 +1887,7 @@
     <t>not available</t>
   </si>
   <si>
-    <t>patient sex</t>
+    <t>patient_sex</t>
   </si>
   <si>
     <t>(Mandatory) Sex of the patient from which the tumor was extracted. if sex is unknown please select “not available”</t>
@@ -2402,7 +2420,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2446,7 +2464,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2473,7 +2491,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3197,6 +3215,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3218,27 +3241,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3258,122 +3281,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3397,120 +3420,120 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>
@@ -3531,7 +3554,7 @@
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S101">
-      <formula1>wasthePDXmodelhumanised</formula1>
+      <formula1>wasthepdxmodelhumanised</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
       <formula1>patientsex</formula1>
@@ -3543,1530 +3566,1555 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:T289"/>
+  <dimension ref="E1:T294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="5:20">
       <c r="E1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="T1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="5:20">
       <c r="E2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="S2" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="T2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="5:20">
       <c r="E3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="S3" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="T3" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="5:20">
       <c r="E4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="5:20">
       <c r="E5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="5:20">
       <c r="E6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="5:20">
       <c r="E7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="5:20">
       <c r="N8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="5:20">
       <c r="N9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="5:20">
       <c r="N10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="5:20">
       <c r="N11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" spans="5:20">
       <c r="N12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="5:20">
       <c r="N13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="5:20">
       <c r="N14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="5:20">
       <c r="N15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="5:20">
       <c r="N16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="14:14">
       <c r="N17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="14:14">
       <c r="N18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="14:14">
       <c r="N19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="14:14">
       <c r="N20" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="14:14">
       <c r="N21" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="14:14">
       <c r="N22" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="14:14">
       <c r="N23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="14:14">
       <c r="N24" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="14:14">
       <c r="N25" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="14:14">
       <c r="N26" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" spans="14:14">
       <c r="N27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="14:14">
       <c r="N28" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="29" spans="14:14">
       <c r="N29" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="14:14">
       <c r="N30" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="31" spans="14:14">
       <c r="N31" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" spans="14:14">
       <c r="N32" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="14:14">
       <c r="N33" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="14:14">
       <c r="N34" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="14:14">
       <c r="N35" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="14:14">
       <c r="N36" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="14:14">
       <c r="N37" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" spans="14:14">
       <c r="N38" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" spans="14:14">
       <c r="N39" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="40" spans="14:14">
       <c r="N40" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="14:14">
       <c r="N41" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" spans="14:14">
       <c r="N42" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" spans="14:14">
       <c r="N43" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" spans="14:14">
       <c r="N44" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="14:14">
       <c r="N45" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="14:14">
       <c r="N46" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="14:14">
       <c r="N47" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="14:14">
       <c r="N48" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="89" spans="14:14">
       <c r="N89" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="90" spans="14:14">
       <c r="N90" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="91" spans="14:14">
       <c r="N91" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="92" spans="14:14">
       <c r="N92" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="93" spans="14:14">
       <c r="N93" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="94" spans="14:14">
       <c r="N94" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="95" spans="14:14">
       <c r="N95" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="96" spans="14:14">
       <c r="N96" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="97" spans="14:14">
       <c r="N97" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="98" spans="14:14">
       <c r="N98" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="99" spans="14:14">
       <c r="N99" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="100" spans="14:14">
       <c r="N100" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101" spans="14:14">
       <c r="N101" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102" spans="14:14">
       <c r="N102" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="103" spans="14:14">
       <c r="N103" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="104" spans="14:14">
       <c r="N104" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="105" spans="14:14">
       <c r="N105" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="106" spans="14:14">
       <c r="N106" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="107" spans="14:14">
       <c r="N107" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="108" spans="14:14">
       <c r="N108" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="109" spans="14:14">
       <c r="N109" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="110" spans="14:14">
       <c r="N110" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="111" spans="14:14">
       <c r="N111" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="112" spans="14:14">
       <c r="N112" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="113" spans="14:14">
       <c r="N113" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="114" spans="14:14">
       <c r="N114" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="115" spans="14:14">
       <c r="N115" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="116" spans="14:14">
       <c r="N116" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="117" spans="14:14">
       <c r="N117" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="118" spans="14:14">
       <c r="N118" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="119" spans="14:14">
       <c r="N119" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="120" spans="14:14">
       <c r="N120" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="121" spans="14:14">
       <c r="N121" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="122" spans="14:14">
       <c r="N122" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="123" spans="14:14">
       <c r="N123" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="124" spans="14:14">
       <c r="N124" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="125" spans="14:14">
       <c r="N125" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="126" spans="14:14">
       <c r="N126" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="127" spans="14:14">
       <c r="N127" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="128" spans="14:14">
       <c r="N128" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="129" spans="14:14">
       <c r="N129" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="130" spans="14:14">
       <c r="N130" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="131" spans="14:14">
       <c r="N131" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="132" spans="14:14">
       <c r="N132" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="133" spans="14:14">
       <c r="N133" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="134" spans="14:14">
       <c r="N134" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="135" spans="14:14">
       <c r="N135" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="136" spans="14:14">
       <c r="N136" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="137" spans="14:14">
       <c r="N137" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="138" spans="14:14">
       <c r="N138" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="139" spans="14:14">
       <c r="N139" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="140" spans="14:14">
       <c r="N140" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="141" spans="14:14">
       <c r="N141" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="142" spans="14:14">
       <c r="N142" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="143" spans="14:14">
       <c r="N143" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="144" spans="14:14">
       <c r="N144" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="145" spans="14:14">
       <c r="N145" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="146" spans="14:14">
       <c r="N146" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="147" spans="14:14">
       <c r="N147" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="148" spans="14:14">
       <c r="N148" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="149" spans="14:14">
       <c r="N149" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="150" spans="14:14">
       <c r="N150" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="151" spans="14:14">
       <c r="N151" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="152" spans="14:14">
       <c r="N152" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="153" spans="14:14">
       <c r="N153" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="154" spans="14:14">
       <c r="N154" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="155" spans="14:14">
       <c r="N155" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="156" spans="14:14">
       <c r="N156" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="157" spans="14:14">
       <c r="N157" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="158" spans="14:14">
       <c r="N158" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="159" spans="14:14">
       <c r="N159" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="160" spans="14:14">
       <c r="N160" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="161" spans="14:14">
       <c r="N161" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="162" spans="14:14">
       <c r="N162" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="163" spans="14:14">
       <c r="N163" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="164" spans="14:14">
       <c r="N164" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="165" spans="14:14">
       <c r="N165" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="166" spans="14:14">
       <c r="N166" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="167" spans="14:14">
       <c r="N167" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="168" spans="14:14">
       <c r="N168" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="169" spans="14:14">
       <c r="N169" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="170" spans="14:14">
       <c r="N170" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="171" spans="14:14">
       <c r="N171" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="172" spans="14:14">
       <c r="N172" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="173" spans="14:14">
       <c r="N173" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="174" spans="14:14">
       <c r="N174" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="175" spans="14:14">
       <c r="N175" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="176" spans="14:14">
       <c r="N176" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="177" spans="14:14">
       <c r="N177" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="178" spans="14:14">
       <c r="N178" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="179" spans="14:14">
       <c r="N179" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="180" spans="14:14">
       <c r="N180" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="181" spans="14:14">
       <c r="N181" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="182" spans="14:14">
       <c r="N182" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="183" spans="14:14">
       <c r="N183" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="184" spans="14:14">
       <c r="N184" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="185" spans="14:14">
       <c r="N185" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="186" spans="14:14">
       <c r="N186" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="187" spans="14:14">
       <c r="N187" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="188" spans="14:14">
       <c r="N188" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="189" spans="14:14">
       <c r="N189" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="190" spans="14:14">
       <c r="N190" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="191" spans="14:14">
       <c r="N191" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="192" spans="14:14">
       <c r="N192" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="193" spans="14:14">
       <c r="N193" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="194" spans="14:14">
       <c r="N194" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="195" spans="14:14">
       <c r="N195" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="196" spans="14:14">
       <c r="N196" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="197" spans="14:14">
       <c r="N197" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="198" spans="14:14">
       <c r="N198" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="199" spans="14:14">
       <c r="N199" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="200" spans="14:14">
       <c r="N200" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="201" spans="14:14">
       <c r="N201" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="202" spans="14:14">
       <c r="N202" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="203" spans="14:14">
       <c r="N203" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="204" spans="14:14">
       <c r="N204" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="205" spans="14:14">
       <c r="N205" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="206" spans="14:14">
       <c r="N206" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="207" spans="14:14">
       <c r="N207" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="208" spans="14:14">
       <c r="N208" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="209" spans="14:14">
       <c r="N209" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="210" spans="14:14">
       <c r="N210" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="211" spans="14:14">
       <c r="N211" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="212" spans="14:14">
       <c r="N212" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="213" spans="14:14">
       <c r="N213" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="214" spans="14:14">
       <c r="N214" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="215" spans="14:14">
       <c r="N215" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="216" spans="14:14">
       <c r="N216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="217" spans="14:14">
       <c r="N217" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="218" spans="14:14">
       <c r="N218" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="219" spans="14:14">
       <c r="N219" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="220" spans="14:14">
       <c r="N220" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="221" spans="14:14">
       <c r="N221" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="222" spans="14:14">
       <c r="N222" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="223" spans="14:14">
       <c r="N223" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="224" spans="14:14">
       <c r="N224" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="225" spans="14:14">
       <c r="N225" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="226" spans="14:14">
       <c r="N226" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="227" spans="14:14">
       <c r="N227" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="228" spans="14:14">
       <c r="N228" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="229" spans="14:14">
       <c r="N229" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="230" spans="14:14">
       <c r="N230" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="231" spans="14:14">
       <c r="N231" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="232" spans="14:14">
       <c r="N232" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="233" spans="14:14">
       <c r="N233" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="234" spans="14:14">
       <c r="N234" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="235" spans="14:14">
       <c r="N235" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="236" spans="14:14">
       <c r="N236" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="237" spans="14:14">
       <c r="N237" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="238" spans="14:14">
       <c r="N238" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="239" spans="14:14">
       <c r="N239" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="240" spans="14:14">
       <c r="N240" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="241" spans="14:14">
       <c r="N241" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="242" spans="14:14">
       <c r="N242" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="243" spans="14:14">
       <c r="N243" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="244" spans="14:14">
       <c r="N244" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="245" spans="14:14">
       <c r="N245" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="246" spans="14:14">
       <c r="N246" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="247" spans="14:14">
       <c r="N247" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="248" spans="14:14">
       <c r="N248" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="249" spans="14:14">
       <c r="N249" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="250" spans="14:14">
       <c r="N250" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="251" spans="14:14">
       <c r="N251" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="252" spans="14:14">
       <c r="N252" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="253" spans="14:14">
       <c r="N253" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="254" spans="14:14">
       <c r="N254" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="255" spans="14:14">
       <c r="N255" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="256" spans="14:14">
       <c r="N256" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="257" spans="14:14">
       <c r="N257" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="258" spans="14:14">
       <c r="N258" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="259" spans="14:14">
       <c r="N259" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="260" spans="14:14">
       <c r="N260" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="261" spans="14:14">
       <c r="N261" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="262" spans="14:14">
       <c r="N262" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="263" spans="14:14">
       <c r="N263" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="264" spans="14:14">
       <c r="N264" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="265" spans="14:14">
       <c r="N265" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="266" spans="14:14">
       <c r="N266" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="267" spans="14:14">
       <c r="N267" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="268" spans="14:14">
       <c r="N268" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="269" spans="14:14">
       <c r="N269" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="270" spans="14:14">
       <c r="N270" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="271" spans="14:14">
       <c r="N271" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="272" spans="14:14">
       <c r="N272" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="273" spans="14:14">
       <c r="N273" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="274" spans="14:14">
       <c r="N274" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="275" spans="14:14">
       <c r="N275" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="276" spans="14:14">
       <c r="N276" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="277" spans="14:14">
       <c r="N277" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="278" spans="14:14">
       <c r="N278" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="279" spans="14:14">
       <c r="N279" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="280" spans="14:14">
       <c r="N280" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="281" spans="14:14">
       <c r="N281" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="282" spans="14:14">
       <c r="N282" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="283" spans="14:14">
       <c r="N283" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="284" spans="14:14">
       <c r="N284" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="285" spans="14:14">
       <c r="N285" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="286" spans="14:14">
       <c r="N286" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="287" spans="14:14">
       <c r="N287" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="288" spans="14:14">
       <c r="N288" t="s">
-        <v>275</v>
+        <v>593</v>
       </c>
     </row>
     <row r="289" spans="14:14">
       <c r="N289" t="s">
-        <v>592</v>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="290" spans="14:14">
+      <c r="N290" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="291" spans="14:14">
+      <c r="N291" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="292" spans="14:14">
+      <c r="N292" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="293" spans="14:14">
+      <c r="N293" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="294" spans="14:14">
+      <c r="N294" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
